--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AANYA JAIN</t>
+          <t>AAYUSH GUPTA</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AARAV DUA</t>
+          <t>AKSHITA PURI</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AAYUSH GUPTA</t>
+          <t>ANSHIKA</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AKSHITA PURI</t>
+          <t>ARNAV SHARMA</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANSHIKA</t>
+          <t>AROUSH SETH</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARNAV SHARMA</t>
+          <t>ARSHIA KHAUND</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AROUSH SETH</t>
+          <t>BHAVYA ARORA</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DIPIN PANDEY</t>
+          <t>DREESHTI KAPOOR</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ISHANI JHA</t>
+          <t>DEVANSH PANDEYA</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAKSHAY MALHOTRA</t>
+          <t>EKAANSH GABA</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KASHIKA TAYAL</t>
+          <t>ISHANI JHA</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAHI WADHWA</t>
+          <t>IHINA ROY</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PANKAJ</t>
+          <t>JIAH BAJAJ</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRATHAM SHARMA</t>
+          <t>MAHI WADHWA</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RANVEER SOLANKI</t>
+          <t>PANKAJ</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RISHABH SINGH</t>
+          <t>PRATHAM SHARMA</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ROUNAK BISWAS</t>
+          <t>RANVEER SOLANKI</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SUMAN</t>
+          <t>RIHIT RAI</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNNABH BHALLA</t>
+          <t>ROUNAK BISWAS</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VANSHIKA ARYA</t>
+          <t>SANYAM MATHUR</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YUVRAJ MALIK</t>
+          <t>SASHVI SINGLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SHARVI SINGHAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SUMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VANSHIKA ARYA</t>
         </is>
       </c>
     </row>
